--- a/docs/Halcyon_Credit_Daily_Dashboard.xlsx
+++ b/docs/Halcyon_Credit_Daily_Dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yash/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yash/CapStone/credit-arbiter/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B300D6C6-451D-3647-A640-72D93DE4890B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233D63A6-909C-1047-BFFA-44E7A76DC6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="254">
   <si>
     <t>Halcyon Credit — Daily Progress Dashboard</t>
   </si>
@@ -203,24 +203,12 @@
     <t>BL-001</t>
   </si>
   <si>
-    <t>A-8b (CODE_GENDER / DAYS_BIRTH exclusion) not yet signed off by Compliance SME</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
-    <t>Drafted the exclusion note ourselves and shared on Slack; treating as confirmed pending writeback</t>
-  </si>
-  <si>
     <t>Open</t>
   </si>
   <si>
-    <t>Need 10 min with Compliance SME tomorrow morning</t>
-  </si>
-  <si>
-    <t>BL-002</t>
-  </si>
-  <si>
     <t>Vector store choice (Chroma vs Pinecone) blocking HL architecture + DB schema</t>
   </si>
   <si>
@@ -233,24 +221,9 @@
     <t>15-min call with Tech Lead to decide before Sprint 1</t>
   </si>
   <si>
-    <t>BL-003</t>
-  </si>
-  <si>
-    <t>Wireframes not started — UX designer pulled to another project</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>UX</t>
-  </si>
-  <si>
-    <t>Sketched low-fi flow on paper (Queue → App Detail → Evidence Panel → Decision)</t>
-  </si>
-  <si>
-    <t>Reassign UX bandwidth tomorrow</t>
-  </si>
-  <si>
     <t>Task ID</t>
   </si>
   <si>
@@ -287,9 +260,6 @@
     <t>Not Started</t>
   </si>
   <si>
-    <t>Blocked by BL-003</t>
-  </si>
-  <si>
     <t>US-008</t>
   </si>
   <si>
@@ -335,21 +305,6 @@
     <t>US-005</t>
   </si>
   <si>
-    <t>A-8b Open-Question Closure</t>
-  </si>
-  <si>
-    <t>Blocked by BL-001</t>
-  </si>
-  <si>
-    <t>US-015</t>
-  </si>
-  <si>
-    <t>DoR &amp; DoD</t>
-  </si>
-  <si>
-    <t>DoR list pending</t>
-  </si>
-  <si>
     <t>US-003</t>
   </si>
   <si>
@@ -380,18 +335,9 @@
     <t>Next Action</t>
   </si>
   <si>
-    <t>A-8b signoff from Compliance SME</t>
-  </si>
-  <si>
     <t>Decision</t>
   </si>
   <si>
-    <t>Unblocks ML feature engineering for Sprint 1</t>
-  </si>
-  <si>
-    <t>10-min call with SME tomorrow AM</t>
-  </si>
-  <si>
     <t>Vector store choice (Chroma vs Pinecone)</t>
   </si>
   <si>
@@ -419,18 +365,6 @@
     <t>Discuss with PM in standup</t>
   </si>
   <si>
-    <t>Publish OpenAPI v0.1</t>
-  </si>
-  <si>
-    <t>Deliverable</t>
-  </si>
-  <si>
-    <t>Backend + UI can parallelise from Sprint 1</t>
-  </si>
-  <si>
-    <t>After US-009 closes</t>
-  </si>
-  <si>
     <t>RAG retrieval accuracy spike plan</t>
   </si>
   <si>
@@ -491,9 +425,6 @@
     <t>HL Architecture</t>
   </si>
   <si>
-    <t>API Contract Definition</t>
-  </si>
-  <si>
     <t>US-012</t>
   </si>
   <si>
@@ -854,9 +785,6 @@
     <t>Abe</t>
   </si>
   <si>
-    <t>Yash, Het</t>
-  </si>
-  <si>
     <t>Abe, Yash, Het</t>
   </si>
   <si>
@@ -864,6 +792,15 @@
   </si>
   <si>
     <t>Yash, Abe, Het</t>
+  </si>
+  <si>
+    <t>Yash, Abe</t>
+  </si>
+  <si>
+    <t>Abe, Yash</t>
+  </si>
+  <si>
+    <t>API Definition</t>
   </si>
 </sst>
 </file>
@@ -873,7 +810,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -928,6 +865,13 @@
       <color rgb="FF1F3A5F"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -993,7 +937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1034,6 +978,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1147,13 +1094,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4A6A6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
@@ -1168,7 +1108,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
+          <fgColor rgb="FFF4A6A6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1196,6 +1136,13 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1204,13 +1151,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF4A6A6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1231,7 +1171,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1245,7 +1185,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4A6A6"/>
+          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1259,7 +1199,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
+          <fgColor rgb="FFF4A6A6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1924,12 +1871,12 @@
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="16">
-        <f>COUNTA(Backlog!A4:A57)</f>
-        <v>54</v>
+        <f>COUNTA(Backlog!A4:A56)</f>
+        <v>53</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="16">
-        <f>COUNTIF(Backlog!H4:H57,"Done")</f>
+        <f>COUNTIF(Backlog!H4:H56,"Done")</f>
         <v>2</v>
       </c>
       <c r="H8" s="17"/>
@@ -1954,23 +1901,23 @@
     </row>
     <row r="11" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16">
-        <f>COUNTIF(Blockers!G4:G50,"Open")+COUNTIF(Blockers!G4:G50,"In Progress")</f>
-        <v>1</v>
+        <f>COUNTIF(Blockers!G3:G48,"Open")+COUNTIF(Blockers!G3:G48,"In Progress")</f>
+        <v>0</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="16">
-        <f>COUNTIF('Pending Tasks'!H4:H100,"Not Started")+COUNTIF('Pending Tasks'!H4:H100,"In Progress")</f>
-        <v>8</v>
+        <f>COUNTIF('Pending Tasks'!H4:H98,"Not Started")+COUNTIF('Pending Tasks'!H4:H98,"In Progress")</f>
+        <v>6</v>
       </c>
       <c r="D11" s="17"/>
       <c r="E11" s="16">
-        <f>COUNTIF('High Priority'!E4:E50,"&lt;&gt;Closed")-COUNTBLANK('High Priority'!E4:E50)</f>
-        <v>3</v>
+        <f>COUNTIF('High Priority'!E3:E48,"&lt;&gt;Closed")-COUNTBLANK('High Priority'!E3:E48)</f>
+        <v>2</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="16">
         <f ca="1">TODAY()-DATE(2026,6,22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="17"/>
     </row>
@@ -2174,7 +2121,7 @@
       </c>
       <c r="F42" s="3">
         <f>COUNTIF(Blockers!G:G,"Open")+COUNTIF(Blockers!G:G,"In Progress")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="3" t="str">
         <f>IFERROR(INDEX('Daily Log'!H:H,MATCH(MAX('Daily Log'!A:A),'Daily Log'!A:A,0)),"—")</f>
@@ -2295,7 +2242,7 @@
         <v>43</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>45</v>
@@ -2899,7 +2846,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2950,78 +2897,32 @@
         <v>46195</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>44</v>
+      <c r="E2" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="7">
-        <v>46195</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="7">
-        <v>46195</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="7"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="9"/>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B4" s="9"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5" s="9"/>
@@ -3395,51 +3296,43 @@
       <c r="B97" s="9"/>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B98" s="9"/>
-      <c r="I98" s="9"/>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B99" s="9"/>
-      <c r="I99" s="9"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D200">
-    <cfRule type="expression" dxfId="31" priority="9">
+  <conditionalFormatting sqref="D2:D198">
+    <cfRule type="expression" dxfId="31" priority="6">
+      <formula>$D2="Critical"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="7">
+      <formula>$D2="High"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="8">
+      <formula>$D2="Medium"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="9">
       <formula>$D2="Low"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="8">
-      <formula>$D2="Medium"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="7">
-      <formula>$D2="High"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="6">
-      <formula>$D2="Critical"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G200">
+  <conditionalFormatting sqref="G2:G198">
     <cfRule type="expression" dxfId="27" priority="1">
       <formula>$G2="Open"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="4">
-      <formula>$G2="Closed"</formula>
+    <cfRule type="expression" dxfId="26" priority="2">
+      <formula>$G2="In Progress"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="25" priority="3">
       <formula>$G2="Resolved"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="2">
-      <formula>$G2="In Progress"</formula>
+    <cfRule type="expression" dxfId="24" priority="4">
+      <formula>$G2="Closed"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="5">
       <formula>$G2="Escalated"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D200" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D198" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G200" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G198" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Open,In Progress,Resolved,Closed,Escalated"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3449,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3464,22 +3357,22 @@
   <sheetData>
     <row r="1" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>18</v>
@@ -3488,7 +3381,7 @@
         <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>39</v>
@@ -3496,19 +3389,19 @@
     </row>
     <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="F2" s="7">
         <v>46196</v>
@@ -3517,30 +3410,30 @@
         <v>0.2</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="F3" s="7">
         <v>46196</v>
@@ -3549,30 +3442,28 @@
         <v>0</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>82</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="F4" s="7">
         <v>46196</v>
@@ -3581,30 +3472,30 @@
         <v>0.2</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>44</v>
+        <v>251</v>
       </c>
       <c r="F5" s="7">
         <v>46196</v>
@@ -3613,30 +3504,30 @@
         <v>0.15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="F6" s="7">
         <v>46196</v>
@@ -3645,27 +3536,27 @@
         <v>0.1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>44</v>
@@ -3677,142 +3568,86 @@
         <v>0</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="F8" s="7">
         <v>46196</v>
       </c>
       <c r="G8" s="5">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>270</v>
+        <v>75</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="F9" s="7">
         <v>46196</v>
       </c>
       <c r="G9" s="5">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="F10" s="7">
-        <v>46196</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="F11" s="7">
-        <v>46196</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>108</v>
-      </c>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F12" s="9"/>
@@ -4558,53 +4393,45 @@
       <c r="F197" s="9"/>
       <c r="G197" s="10"/>
     </row>
-    <row r="198" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F198" s="9"/>
-      <c r="G198" s="10"/>
-    </row>
-    <row r="199" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F199" s="9"/>
-      <c r="G199" s="10"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F300">
+  <conditionalFormatting sqref="F2:F298">
     <cfRule type="expression" dxfId="22" priority="8">
       <formula>AND($F2&lt;&gt;"",$F2&lt;TODAY(),$H2&lt;&gt;"Done")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H300">
-    <cfRule type="expression" dxfId="21" priority="2">
+  <conditionalFormatting sqref="H2:H298">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>$H2="Done"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>$H2="In Progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="3">
+    <cfRule type="expression" dxfId="19" priority="3">
       <formula>$H2="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="4">
+    <cfRule type="expression" dxfId="18" priority="4">
       <formula>$H2="Not Started"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="1">
-      <formula>$H2="Done"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I298">
+    <cfRule type="expression" dxfId="17" priority="5">
+      <formula>$I2="High"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I300">
-    <cfRule type="expression" dxfId="17" priority="6">
+    <cfRule type="expression" dxfId="16" priority="6">
       <formula>$I2="Medium"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="7">
+    <cfRule type="expression" dxfId="15" priority="7">
       <formula>$I2="Low"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5">
-      <formula>$I2="High"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H300" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H298" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Done,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I300" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I298" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C300" xr:uid="{00000000-0002-0000-0300-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C298" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"Sprint 0,Sprint 1,Sprint 2,Sprint 3,Sprint 4"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4614,7 +4441,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -4628,141 +4455,101 @@
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="D2" s="7">
         <v>46196</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D3" s="7">
         <v>46196</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D4" s="7">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="7">
-        <v>46196</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="7">
-        <v>46197</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>134</v>
-      </c>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D7" s="9"/>
@@ -5037,19 +4824,13 @@
     <row r="97" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D97" s="9"/>
     </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D98" s="9"/>
-    </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D99" s="9"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D200">
+  <conditionalFormatting sqref="D2:D198">
     <cfRule type="expression" dxfId="14" priority="6">
       <formula>AND($D2&lt;&gt;"",$D2&lt;TODAY(),$E2&lt;&gt;"Done",$E2&lt;&gt;"Closed")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E200">
+  <conditionalFormatting sqref="E2:E198">
     <cfRule type="expression" dxfId="13" priority="1">
       <formula>$E2="Done"</formula>
     </cfRule>
@@ -5067,10 +4848,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E200" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E198" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Not Started,Open,In Progress,Done,Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B200" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B198" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"Decision,Deliverable,Risk,Resource,Compliance,Tech"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5111,16 +4892,16 @@
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>19</v>
@@ -5320,7 +5101,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I199"/>
+  <dimension ref="A1:I198"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5335,7 +5116,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -5348,22 +5129,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
         <v>35</v>
@@ -5377,22 +5158,22 @@
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>35</v>
@@ -5406,13 +5187,13 @@
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>8</v>
@@ -5421,13 +5202,13 @@
         <v>3</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>270</v>
+        <v>54</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I4" s="5">
         <v>0.75</v>
@@ -5435,13 +5216,13 @@
     </row>
     <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
@@ -5450,13 +5231,13 @@
         <v>3</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>271</v>
+        <v>54</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I5" s="5">
         <v>0.7</v>
@@ -5464,13 +5245,13 @@
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>8</v>
@@ -5479,13 +5260,13 @@
         <v>3</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I6" s="5">
         <v>0.3</v>
@@ -5493,13 +5274,13 @@
     </row>
     <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>8</v>
@@ -5508,13 +5289,13 @@
         <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>271</v>
+        <v>54</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>248</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I7" s="5">
         <v>0.6</v>
@@ -5522,13 +5303,13 @@
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>8</v>
@@ -5537,13 +5318,13 @@
         <v>2</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>270</v>
+        <v>54</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>247</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I8" s="5">
         <v>0.4</v>
@@ -5551,13 +5332,13 @@
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>8</v>
@@ -5566,13 +5347,13 @@
         <v>3</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I9" s="5">
         <v>0.2</v>
@@ -5580,13 +5361,13 @@
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>8</v>
@@ -5595,13 +5376,13 @@
         <v>3</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>67</v>
+        <v>249</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -5609,13 +5390,13 @@
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>8</v>
@@ -5624,13 +5405,13 @@
         <v>3</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I11" s="5">
         <v>0.2</v>
@@ -5638,13 +5419,13 @@
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>8</v>
@@ -5653,13 +5434,13 @@
         <v>3</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>44</v>
+        <v>251</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I12" s="5">
         <v>0.15</v>
@@ -5667,13 +5448,13 @@
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>8</v>
@@ -5682,13 +5463,13 @@
         <v>3</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I13" s="5">
         <v>0.1</v>
@@ -5696,13 +5477,13 @@
     </row>
     <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>150</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>8</v>
@@ -5711,13 +5492,13 @@
         <v>3</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>44</v>
+        <v>252</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I14" s="5">
         <v>0</v>
@@ -5725,13 +5506,13 @@
     </row>
     <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>8</v>
@@ -5740,13 +5521,13 @@
         <v>2</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I15" s="5">
         <v>0.85</v>
@@ -5754,13 +5535,13 @@
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>8</v>
@@ -5769,13 +5550,13 @@
         <v>3</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>44</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="I16" s="5">
         <v>1</v>
@@ -5783,13 +5564,13 @@
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>8</v>
@@ -5798,13 +5579,13 @@
         <v>2</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>44</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="I17" s="5">
         <v>1</v>
@@ -5812,42 +5593,40 @@
     </row>
     <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E18" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>270</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I18" s="5">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>21</v>
@@ -5856,11 +5635,11 @@
         <v>3</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
@@ -5868,26 +5647,26 @@
     </row>
     <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
@@ -5895,26 +5674,26 @@
     </row>
     <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E21" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I21" s="5">
         <v>0</v>
@@ -5922,26 +5701,26 @@
     </row>
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
@@ -5949,13 +5728,13 @@
     </row>
     <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>21</v>
@@ -5964,11 +5743,11 @@
         <v>5</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
@@ -5976,13 +5755,13 @@
     </row>
     <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>21</v>
@@ -5991,11 +5770,11 @@
         <v>5</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I24" s="5">
         <v>0</v>
@@ -6003,26 +5782,26 @@
     </row>
     <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
@@ -6030,13 +5809,13 @@
     </row>
     <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>21</v>
@@ -6045,11 +5824,11 @@
         <v>3</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
@@ -6057,26 +5836,26 @@
     </row>
     <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E27" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I27" s="5">
         <v>0</v>
@@ -6084,26 +5863,26 @@
     </row>
     <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E28" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
@@ -6111,26 +5890,26 @@
     </row>
     <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E29" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
@@ -6138,26 +5917,26 @@
     </row>
     <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E30" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I30" s="5">
         <v>0</v>
@@ -6165,13 +5944,13 @@
     </row>
     <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>23</v>
@@ -6180,11 +5959,11 @@
         <v>5</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I31" s="5">
         <v>0</v>
@@ -6192,13 +5971,13 @@
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>23</v>
@@ -6207,11 +5986,11 @@
         <v>5</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I32" s="5">
         <v>0</v>
@@ -6219,13 +5998,13 @@
     </row>
     <row r="33" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>23</v>
@@ -6234,11 +6013,11 @@
         <v>5</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I33" s="5">
         <v>0</v>
@@ -6246,26 +6025,26 @@
     </row>
     <row r="34" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
@@ -6273,26 +6052,26 @@
     </row>
     <row r="35" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>199</v>
+        <v>146</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E35" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I35" s="5">
         <v>0</v>
@@ -6300,26 +6079,26 @@
     </row>
     <row r="36" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I36" s="5">
         <v>0</v>
@@ -6327,26 +6106,26 @@
     </row>
     <row r="37" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>204</v>
+        <v>137</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E37" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I37" s="5">
         <v>0</v>
@@ -6354,26 +6133,26 @@
     </row>
     <row r="38" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E38" s="4">
         <v>3</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I38" s="5">
         <v>0</v>
@@ -6381,26 +6160,26 @@
     </row>
     <row r="39" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I39" s="5">
         <v>0</v>
@@ -6408,13 +6187,13 @@
     </row>
     <row r="40" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>25</v>
@@ -6423,11 +6202,11 @@
         <v>8</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I40" s="5">
         <v>0</v>
@@ -6435,13 +6214,13 @@
     </row>
     <row r="41" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>25</v>
@@ -6450,11 +6229,11 @@
         <v>8</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I41" s="5">
         <v>0</v>
@@ -6462,26 +6241,26 @@
     </row>
     <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I42" s="5">
         <v>0</v>
@@ -6489,26 +6268,26 @@
     </row>
     <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I43" s="5">
         <v>0</v>
@@ -6516,13 +6295,13 @@
     </row>
     <row r="44" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>221</v>
+        <v>151</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>25</v>
@@ -6531,11 +6310,11 @@
         <v>5</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I44" s="5">
         <v>0</v>
@@ -6543,26 +6322,26 @@
     </row>
     <row r="45" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I45" s="5">
         <v>0</v>
@@ -6570,26 +6349,26 @@
     </row>
     <row r="46" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>221</v>
+        <v>68</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I46" s="5">
         <v>0</v>
@@ -6597,26 +6376,26 @@
     </row>
     <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E47" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I47" s="5">
         <v>0</v>
@@ -6624,26 +6403,26 @@
     </row>
     <row r="48" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E48" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I48" s="5">
         <v>0</v>
@@ -6651,13 +6430,13 @@
     </row>
     <row r="49" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>27</v>
@@ -6666,11 +6445,11 @@
         <v>5</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I49" s="5">
         <v>0</v>
@@ -6678,13 +6457,13 @@
     </row>
     <row r="50" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>27</v>
@@ -6693,11 +6472,11 @@
         <v>5</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I50" s="5">
         <v>0</v>
@@ -6705,13 +6484,13 @@
     </row>
     <row r="51" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>27</v>
@@ -6720,11 +6499,11 @@
         <v>5</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I51" s="5">
         <v>0</v>
@@ -6732,26 +6511,26 @@
     </row>
     <row r="52" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>221</v>
+        <v>137</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E52" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I52" s="5">
         <v>0</v>
@@ -6759,26 +6538,26 @@
     </row>
     <row r="53" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E53" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I53" s="5">
         <v>0</v>
@@ -6786,26 +6565,26 @@
     </row>
     <row r="54" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E54" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I54" s="5">
         <v>0</v>
@@ -6813,26 +6592,26 @@
     </row>
     <row r="55" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E55" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I55" s="5">
         <v>0</v>
@@ -6840,13 +6619,13 @@
     </row>
     <row r="56" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>27</v>
@@ -6855,42 +6634,18 @@
         <v>3</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I56" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E57" s="4">
-        <v>3</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I57" s="5">
-        <v>0</v>
-      </c>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I57" s="10"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="I58" s="10"/>
@@ -7314,15 +7069,12 @@
     </row>
     <row r="198" spans="9:9" x14ac:dyDescent="0.2">
       <c r="I198" s="10"/>
-    </row>
-    <row r="199" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I199" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:H300">
+  <conditionalFormatting sqref="H4:H299">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>$H4="Done"</formula>
     </cfRule>
@@ -7337,10 +7089,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="H4:H300" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H4:H299" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Done,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F4:F300" xr:uid="{00000000-0002-0000-0600-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F4:F299" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7358,7 +7110,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -7371,32 +7123,32 @@
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -7404,7 +7156,7 @@
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -7412,27 +7164,27 @@
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
@@ -7440,7 +7192,7 @@
     </row>
     <row r="18" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
@@ -7448,42 +7200,42 @@
     </row>
     <row r="20" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
